--- a/outputs/tables/Regression_Results_NDBI_Pooled_DistrictCluster.xlsx
+++ b/outputs/tables/Regression_Results_NDBI_Pooled_DistrictCluster.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,21 +443,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Outcome: Delta NDBI = NDBI_t - NDBI_{t-1} (level change; NDBI is bounded in [-1,1]).</t>
+          <t>Outcome: NDBI_t (level; NDBI is bounded in [-1,1]).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lagged regressors: NDVI_{t-1}, NL_{t-1}. Flood (Seasonal_Ratio) is contemporaneous.</t>
+          <t>Regressors: Seasonal_Ratio (contemp.), NDVI_{t-1}, NL_{t-1}, NDBI_{t-1} (lagged DV).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Two-way fixed effects: AC (entity) + YEAR (time). Constant absorbed by FE; reported beta_0 is the implied intercept.</t>
+          <t>Two-way FE: AC (entity) + YEAR (time). Constant is explicit; FE absorbed by PanelOLS.</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sample: 2016-2019 (need t-1 covariates).</t>
+          <t>Nickell bias: lagged NDBI_{t-1} with entity FE biases its coefficient ~1/T ≈ 20%; flood coef far less affected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cross-check: same specification as run_ndbi_ols_pooled.py (pyfixest); coefficients should be close.</t>
         </is>
       </c>
     </row>
@@ -486,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +530,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1692</v>
+        <v>-0.1253</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -531,7 +538,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.1189</v>
+        <v>-0.1384</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -546,19 +553,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0487</v>
+        <v>-0.0157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.0396</v>
+        <v>-0.0133</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
     </row>
@@ -569,19 +576,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.0024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3828</v>
+        <v>0.0036</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
     </row>
@@ -592,19 +599,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0003</v>
+        <v>0.0013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>p &lt; 0.01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0012</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>p &lt; 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NDBI_median_t_minus_1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.0577</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>p &lt; 0.10</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06510000000000001</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>p &lt; 0.05</t>
         </is>
       </c>
     </row>
@@ -619,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,22 +711,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.1691751342684578</v>
+        <v>-0.1252930261531307</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03516810103248895</v>
+        <v>0.01105079125337055</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.81047111733928</v>
+        <v>-11.33792352786645</v>
       </c>
       <c r="F2" t="n">
-        <v>1.577179156608821e-06</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2381301043080435</v>
+        <v>-0.1469605900048093</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1002201642288721</v>
+        <v>-0.1036254623014521</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -716,26 +746,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.04874133932750782</v>
+        <v>-0.01573178629631175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01352557803408277</v>
+        <v>0.01038158031296362</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.603641870586655</v>
+        <v>-1.515355641632638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003186937561223679</v>
+        <v>0.1297837283424033</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.07526127645026151</v>
+        <v>-0.03608721145592284</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02222140220475413</v>
+        <v>0.004623638863299324</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
     </row>
@@ -751,26 +781,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5306511688452153</v>
+        <v>0.002369791119556105</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09742276876019369</v>
+        <v>0.03049630036123012</v>
       </c>
       <c r="E4" t="n">
-        <v>5.446890656037646</v>
+        <v>0.07770749538422095</v>
       </c>
       <c r="F4" t="n">
-        <v>5.523798130013802e-08</v>
+        <v>0.9380657176888967</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3396319240237043</v>
+        <v>-0.05742507063890683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7216704136667265</v>
+        <v>0.06216465287801904</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
     </row>
@@ -786,26 +816,61 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.0003233219485180386</v>
+        <v>0.00127081986999927</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00101314457513593</v>
+        <v>0.0004322885963598047</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3191271576168285</v>
+        <v>2.939748771308172</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7496514611770699</v>
+        <v>0.003308922330558017</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002309819705668122</v>
+        <v>0.0004232207660779363</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001663175808632045</v>
+        <v>0.002118418973920604</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>p &lt; 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDBI_median_t_minus_1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.05770243138420056</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02972603105752587</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.941141461923884</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05233111865486628</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.1159870067805074</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0005821440121062393</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>p &lt; 0.10</t>
         </is>
       </c>
     </row>
@@ -855,7 +920,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NDBI_median_t - NDBI_median_(t-1) = b0 + b1*Seasonal_Ratio + b2*NDVI_median_(t-1) + b3*NL_median_(t-1) + a_i + g_t + e_it</t>
+          <t>NDBI_median_it = b0 + b1*Seasonal_Ratio + b2*NDVI_median_(t-1) + b3*NL_median_(t-1) + b4*NDBI_median_(t-1) + a_i + g_t + e_it</t>
         </is>
       </c>
     </row>
@@ -867,7 +932,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Two-way FE (PanelOLS) with explicit constant</t>
+          <t>Two-way FE (linearmodels PanelOLS) — cross-check of pyfixest primary (LDV spec)</t>
         </is>
       </c>
     </row>
@@ -944,7 +1009,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2131240283309491</v>
+        <v>-0.01636422186099118</v>
       </c>
     </row>
     <row r="12">
@@ -954,7 +1019,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-3.537741002714364</v>
+        <v>-0.1310009530174905</v>
       </c>
     </row>
     <row r="13">
@@ -964,7 +1029,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4520542514612285</v>
+        <v>-0.1222985382616559</v>
       </c>
     </row>
     <row r="14">
@@ -974,7 +1039,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.31677073737819</v>
+        <v>4.033663153631622</v>
       </c>
     </row>
     <row r="15">
@@ -984,7 +1049,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>0.00289017423985205</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1060,22 +1125,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.1189043062526751</v>
+        <v>-0.1384345527136445</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03705916793493054</v>
+        <v>0.009823614902069655</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.208499080752444</v>
+        <v>-14.09201745932436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001347814596803332</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1915671381833606</v>
+        <v>-0.1576959610838347</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04624147432198962</v>
+        <v>-0.1191731443434544</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1095,26 +1160,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.03958013742876356</v>
+        <v>-0.01325680952973266</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01423793263761974</v>
+        <v>0.009153408568548484</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.779907619746996</v>
+        <v>-1.448292123142371</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005470044797117435</v>
+        <v>0.1476359168983257</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.06749680593314841</v>
+        <v>-0.03120412751558585</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01166346892437871</v>
+        <v>0.004690508456120537</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
     </row>
@@ -1130,26 +1195,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3827527907344983</v>
+        <v>0.003553191323878911</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1044083177660096</v>
+        <v>0.02545001756554946</v>
       </c>
       <c r="E4" t="n">
-        <v>3.665922398944202</v>
+        <v>0.139614493967529</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0002505576210729554</v>
+        <v>0.888973605382738</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1780368063033877</v>
+        <v>-0.04634729706510348</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5874687751656089</v>
+        <v>0.05345367971286131</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>p &lt; 0.01</t>
+          <t>n.s.</t>
         </is>
       </c>
     </row>
@@ -1165,26 +1230,61 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.0005738750166587054</v>
+        <v>0.001246361140823863</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009549746383072823</v>
+        <v>0.0003464977322207363</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.600932206614318</v>
+        <v>3.597025391294245</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5479288072609867</v>
+        <v>0.0003268748140552447</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002446317532454743</v>
+        <v>0.0005669743380856663</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001298567499137332</v>
+        <v>0.001925747943562059</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>p &lt; 0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDBI_mean_t_minus_1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.06505664512519146</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.03195009733928246</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.036195521858542</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04181507227019932</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.1277020031175525</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.002411287132830467</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>p &lt; 0.05</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1334,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NDBI_mean_t - NDBI_mean_(t-1) = b0 + b1*Seasonal_Ratio + b2*NDVI_mean_(t-1) + b3*NL_mean_(t-1) + a_i + g_t + e_it</t>
+          <t>NDBI_mean_it = b0 + b1*Seasonal_Ratio + b2*NDVI_mean_(t-1) + b3*NL_mean_(t-1) + b4*NDBI_mean_(t-1) + a_i + g_t + e_it</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1346,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Two-way FE (PanelOLS) with explicit constant</t>
+          <t>Two-way FE (linearmodels PanelOLS) — cross-check of pyfixest primary (LDV spec)</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1423,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1564590284898397</v>
+        <v>-0.02550946352550665</v>
       </c>
     </row>
     <row r="12">
@@ -1333,7 +1433,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2.806296651896866</v>
+        <v>-0.1511892659401119</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1443,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.3496359492729351</v>
+        <v>-0.140896396447008</v>
       </c>
     </row>
     <row r="14">
@@ -1353,7 +1453,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.92444656139821</v>
+        <v>6.035801798540323</v>
       </c>
     </row>
     <row r="15">
@@ -1363,7 +1463,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.203822042050717e-09</v>
+        <v>7.776756158084375e-05</v>
       </c>
     </row>
   </sheetData>
